--- a/data/output/evaluasi_71.xlsx
+++ b/data/output/evaluasi_71.xlsx
@@ -8,17 +8,20 @@
   </bookViews>
   <sheets>
     <sheet name="7100" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="7101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="7102" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="7104" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="7105" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="7106" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7107" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="7110" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="7111" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="7172" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="7174" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="7109" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7106" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="7104" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="7105" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="7108" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="7110" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7172" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7173" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="7102" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="7109" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="7171" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="7174" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7103" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="7111" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="7107" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +489,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-8.715034499339957</v>
+        <v>-8.715034499490974</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -495,7 +498,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -510,20 +513,160 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-8.91421072152758</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sulawesi Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0.7334014798389064</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="D4" t="n">
+        <v>13.4318911138614</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sulawesi Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.121826558217027</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sulawesi Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.08596739346029314</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sulawesi Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2756790097397459</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>71</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sulawesi Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.054721207154576</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -538,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,57 +718,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7172</v>
+        <v>7109</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Bitung</t>
+          <t>Kabupaten Minahasa Tenggara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-799.330754314</v>
+        <v>0.06760017500206006</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7172</v>
+        <v>7109</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Bitung</t>
+          <t>Kabupaten Minahasa Tenggara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-682.136915083</v>
+        <v>-0.1142696174668169</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7109</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.9473583587547185</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -640,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,85 +848,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7174</v>
+        <v>7171</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Kotamobagu</t>
+          <t>Kota Manado</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-24.16751614</v>
+        <v>0.4461289930584861</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7174</v>
+        <v>7171</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Kotamobagu</t>
+          <t>Kota Manado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-13.190334492</v>
+        <v>8.42741728535681</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>7174</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kota Kotamobagu</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.001850661949937616</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -770,6 +913,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-6.005758937912153</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3582176538389658</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7174</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.2760924983072861</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9.346275452382965</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.879722816129209</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.997042752201811</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -807,29 +1210,131 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7109</v>
+        <v>7111</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa Tenggara</t>
+          <t>Kabupaten Bolaang Mongondow Timur</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.081556200918066</v>
+        <v>-0.1927347067546997</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.859841284617877</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7107</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.110013729133151</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -844,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,169 +1386,225 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7101</v>
+        <v>7106</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow</t>
+          <t>Kabupaten Minahasa Utara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-20.14529</v>
+        <v>-0.04815359711555874</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_net_ekspor_q2-25_ril vs sog_q_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7101</v>
+        <v>7106</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow</t>
+          <t>Kabupaten Minahasa Utara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-11.345107</v>
+        <v>-0.7860813557821346</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7101</v>
+        <v>7106</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow</t>
+          <t>Kabupaten Minahasa Utara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.0006930411232488534</v>
+        <v>19.01665471839132</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7101</v>
+        <v>7106</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow</t>
+          <t>Kabupaten Minahasa Utara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9010641529803104</v>
+        <v>9.354000170412077</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7101</v>
+        <v>7106</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow</t>
+          <t>Kabupaten Minahasa Utara</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.004860381397047672</v>
+        <v>-0.5820097161836955</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7101</v>
+        <v>7106</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow</t>
+          <t>Kabupaten Minahasa Utara</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.004417040487346915</v>
+        <v>-1.571128199619308</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3182926940843902</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7106</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3356151963702055</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1095,169 +1656,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7102</v>
+        <v>7104</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa</t>
+          <t>Kabupaten Kepulauan Talaud</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-27.73979255</v>
+        <v>1.35998381500955</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7102</v>
+        <v>7104</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa</t>
+          <t>Kabupaten Kepulauan Talaud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-18.03403148</v>
+        <v>9.246640213458507</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7102</v>
+        <v>7104</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa</t>
+          <t>Kabupaten Kepulauan Talaud</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.0004575084605073591</v>
+        <v>-0.07433884702815234</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>7102</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Minahasa</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5825978519120075</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>7102</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Minahasa</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.001510993372284271</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>7102</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Minahasa</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.001594955924160859</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1309,113 +1786,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7104</v>
+        <v>7105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Talaud</t>
+          <t>Kabupaten Minahasa Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-299.7683087</v>
+        <v>-3.862521709513507</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7104</v>
+        <v>7105</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Talaud</t>
+          <t>Kabupaten Minahasa Selatan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-205.74</v>
+        <v>-4.822381564524193</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7104</v>
+        <v>7105</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Talaud</t>
+          <t>Kabupaten Minahasa Selatan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.901783209381139</v>
+        <v>-2.486518543633305</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>7104</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Kepulauan Talaud</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.3621327197622958</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1467,57 +1916,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7105</v>
+        <v>7108</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa Selatan</t>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-148.07</v>
+        <v>-14.75233449621927</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7105</v>
+        <v>7108</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa Selatan</t>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-91.11</v>
+        <v>9.831569220377084</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.05908235916206816</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7108</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.924872192398</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1532,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,253 +2074,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7106</v>
+        <v>7110</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa Utara</t>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-61.09999999</v>
+        <v>0.1000000000077529</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7106</v>
+        <v>7110</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa Utara</t>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-38.42999999</v>
+        <v>-0.3657597382716026</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7106</v>
+        <v>7110</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa Utara</t>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.001182833797068571</v>
+        <v>-0.3679524733441548</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7106</v>
+        <v>7110</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa Utara</t>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.618727070423329</v>
+        <v>-0.1899721514481098</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7106</v>
+        <v>7110</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Minahasa Utara</t>
+          <t>Kabupaten Bolaang Mongondow Selatan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.618727070423329</v>
+        <v>-0.2908198019910738</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>7106</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Minahasa Utara</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.01114614802057578</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7106</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Minahasa Utara</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.003007025370670454</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7106</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Minahasa Utara</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1171663206026343</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>7106</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kabupaten Minahasa Utara</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.003115944110429248</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1830,7 +2223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1867,141 +2260,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7107</v>
+        <v>7172</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Utara</t>
+          <t>Kota Bitung</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-24.25062869</v>
+        <v>-3.660195047937093</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7107</v>
+        <v>7172</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Utara</t>
+          <t>Kota Bitung</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-14.419736397</v>
+        <v>-1.46660085702382</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7107</v>
+        <v>7172</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Utara</t>
+          <t>Kota Bitung</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.002728894932722157</v>
+        <v>-0.2888636697673839</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>7107</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Bolaang Mongondow Utara</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.01355220814118143</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>7107</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Bolaang Mongondow Utara</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.01371889701453738</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,141 +2390,169 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7110</v>
+        <v>7173</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Selatan</t>
+          <t>Kota Tomohon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.54099</v>
+        <v>-3.676427139846163</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7110</v>
+        <v>7173</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Selatan</t>
+          <t>Kota Tomohon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.35187</v>
+        <v>-1.360312149932465</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7110</v>
+        <v>7173</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Selatan</t>
+          <t>Kota Tomohon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-7.290014690981683e-05</v>
+        <v>-0.4991022503678708</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7110</v>
+        <v>7173</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Selatan</t>
+          <t>Kota Tomohon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1021841589535875</v>
+        <v>-1.474290945737169</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7110</v>
+        <v>7173</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Selatan</t>
+          <t>Kota Tomohon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.001572791010991955</v>
+        <v>-0.6419111801360533</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7173</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.3060343474005138</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2239,85 +2604,225 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7111</v>
+        <v>7102</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Timur</t>
+          <t>Kabupaten Minahasa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.7012607</v>
+        <v>-8.091398411505931</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7111</v>
+        <v>7102</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Timur</t>
+          <t>Kabupaten Minahasa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.345370743</v>
+        <v>-0.03181425879480713</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7111</v>
+        <v>7102</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Bolaang Mongondow Timur</t>
+          <t>Kabupaten Minahasa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.0002506596433099092</v>
+        <v>-0.09791052843884351</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5407296473288179</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.5990636862628267</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.165347181742407</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.182511153855539</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Minahasa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.01476447606096675</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_71.xlsx
+++ b/data/output/evaluasi_71.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
